--- a/Assets/Resources/Configs/SkillConfig.xlsx
+++ b/Assets/Resources/Configs/SkillConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProgram\SoulFighterSurvivor\Assets\Resources\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068236DC-3E4D-4606-A05A-C4D93F9424D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC18A0C-8E89-4E59-9DAE-7BBCF10E320D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="25845" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="138">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -75,18 +75,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[65,70,75,80,85]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[7,7,7,7,7]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[40,40,40,40,40]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[9,8,7,6,5]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -99,18 +91,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[70,70,70,70,70]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[12,12,12,12,12]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[100,100,100]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[130,105,80]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -199,10 +183,6 @@
   </si>
   <si>
     <t>[75,95,115,135,155],[0.28,0.32,0.36,0.4,0.44]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[40,38,36,34,32]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -216,10 +196,6 @@
   </si>
   <si>
     <t>[60,90,120,150,180]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[40,55,70,85,100]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -528,10 +504,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[60,60,60,60,60]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[20,18,16,14,12]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -541,10 +513,6 @@
   </si>
   <si>
     <t>[50,60,70,80,90],[0.2,0.25,0.3,0.35,0.4]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[100,50,0]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -578,6 +546,46 @@
   </si>
   <si>
     <t xml:space="preserve">莎弥拉只能在她当前的评价等级为S时使用这个技能。使用这个技能会消耗掉所有评价等级。 莎弥拉的武器倾泻出大量的子弹，狂野地在2秒里持续对她周围的所有敌人进行10次射击，每次射击造成&lt;color=#FF6A6A&gt;{0:F0}物理伤害&lt;/color&gt;并施加66.6%效能的生命偷取。这些射击也可以产生暴击。 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[32,35,37,40,42]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[20,20,20,20,20]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[35,35,35,35,35]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[50,50,50]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[20,19,18,17,16]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[20,27,35,42,50]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[20,25,30,35,40]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[20,17,15,12,10]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[20,15,10,5,0]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[50,20,0]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -917,75 +925,75 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="S1" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -1003,60 +1011,60 @@
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
@@ -1074,126 +1082,126 @@
         <v>11</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="L3" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="250.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="M4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q4" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="N4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="O4" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="S4" s="1" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
@@ -1204,138 +1212,138 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1">
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>128</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>14</v>
+        <v>129</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>48</v>
+        <v>133</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>48</v>
+        <v>134</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="N6" s="1">
         <v>0</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="S6" s="1">
         <v>0</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
@@ -1346,67 +1354,67 @@
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="K7" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="N7" s="1">
         <v>0</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="S7" s="1">
         <v>0</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
@@ -1417,67 +1425,67 @@
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="L8" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="N8" s="1">
         <v>0</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S8" s="1">
         <v>0</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1553,7 +1561,7 @@
     </row>
     <row r="10" spans="1:23" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B10" s="1">
         <v>0</v>
@@ -1624,7 +1632,7 @@
     </row>
     <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B11" s="1">
         <v>0</v>
@@ -1695,7 +1703,7 @@
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B12" s="1">
         <v>0</v>
@@ -1766,7 +1774,7 @@
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B13" s="1">
         <v>0</v>

--- a/Assets/Resources/Configs/SkillConfig.xlsx
+++ b/Assets/Resources/Configs/SkillConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProgram\SoulFighterSurvivor\Assets\Resources\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC18A0C-8E89-4E59-9DAE-7BBCF10E320D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CDB8B9E-F417-4F74-A3F1-3FDEB23CC9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="25845" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="111">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -135,96 +135,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Ryze</t>
-  </si>
-  <si>
-    <t>Ryze</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奥术专精</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ArcaneMastery</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>超负荷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Overload</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RunePrison</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpellFlux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>曲境折跃</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>法术涌动</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>符文禁锢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RealmWarp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[75,95,115,135,155],[0.28,0.32,0.36,0.4,0.44]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[6,6,6,6,6]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>瑞兹造成{0}魔法伤害和持续1.5秒的50%减速。
-如果目标带有涌动，则它会将其消耗，使这个技能造成禁锢而非减速。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[60,90,120,150,180]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[13,12,11,10,9]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>瑞兹发射一颗法球，造成{0}魔法伤害并施加持续4秒的涌动给目标和附近的敌人们。
-已被涌动影响的敌人们将使其进一步扩散。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[3.25,3,2.75,2.5,2.25]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>被动：超负荷对带有涌动的目标的伤害加成提升至{0}。 
-主动：瑞兹开启一个前往另一个位置的传送门。在2秒后，传送门附近的所有友军都会被传送到该位置。 如果瑞兹被定身或限制，那么传送门就会被取消。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[0.5,0.75,1]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[210,180,150]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[40,65,90,115,140],[40,65,90,115,140]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -262,10 +172,6 @@
   </si>
   <si>
     <t>_destinationDistance</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>瑞兹每拥有&lt;color=#7700BB&gt;100法术强度&lt;/color&gt;获得&lt;color=#33FFFF&gt;10%最大法力值&lt;/color&gt;。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -274,13 +180,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>被动：符文禁锢和法术涌动会刷新这个技能的冷却时间并充能一枚符文，持续4秒(最多2枚符文)。 
-主动：瑞兹释放一次魔爆，对命中的第一个敌人造成{0:F0}魔法伤害。
-如果目标带有涌动，则它会将其消耗，使这个技能造成10%伤害提升并弹射至附近带有涌动的敌人们。 
-如果2枚符文已被充能，瑞兹就会释放所有符文的能量，来为瑞兹提供持续2秒的{1}移动速度。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>阿狸释放出3团狐火来追踪附近的敌人们并造成&lt;color=#7700BB&gt;{0:F0}魔法伤害&lt;/color&gt;，第一团之后的狐火降低至&lt;color=#7700BB&gt;{1:F0}伤害&lt;/color&gt;（40%）。她还会获得在2秒里持续衰减的&lt;color=#FDF9C8&gt;40%移动速度&lt;/color&gt;。 
 狐火会优先攻击最近的敌人。20%生命值以下的敌人会受到200%伤害。</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -562,18 +461,6 @@
   </si>
   <si>
     <t>[50,50,50]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[20,19,18,17,16]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[20,27,35,42,50]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[20,25,30,35,40]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -914,13 +801,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W13"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultColWidth="29.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="29.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -940,58 +827,43 @@
         <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -1011,58 +883,43 @@
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -1082,129 +939,99 @@
         <v>11</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="250.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="250.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>102</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q4" s="1" t="s">
         <v>99</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -1212,70 +1039,55 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>51</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="V5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W5" s="1" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
@@ -1283,70 +1095,55 @@
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
+        <v>107</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>133</v>
+        <v>42</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>134</v>
+        <v>62</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>131</v>
+        <v>62</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N6" s="1">
         <v>0</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="S6" s="1">
-        <v>0</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="V6" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="W6" s="1" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
@@ -1365,59 +1162,44 @@
       <c r="F7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="1">
-        <v>0</v>
+      <c r="G7" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="N7" s="1">
         <v>0</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="S7" s="1">
-        <v>0</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -1425,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>14</v>
@@ -1436,59 +1218,44 @@
       <c r="F8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="1">
-        <v>0</v>
+      <c r="G8" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I8" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
       <c r="J8" s="1" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="N8" s="1">
         <v>0</v>
       </c>
       <c r="O8" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="P8" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="P8" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="Q8" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="R8" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="R8" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="S8" s="1">
-        <v>0</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="W8" s="1" t="s">
-        <v>120</v>
-      </c>
     </row>
-    <row r="9" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1511,57 +1278,42 @@
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I9" s="1">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="K9" s="1">
-        <v>3000</v>
+        <v>180</v>
       </c>
       <c r="L9" s="1">
-        <v>0</v>
+        <v>475</v>
       </c>
       <c r="M9" s="1">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="N9" s="1">
         <v>0</v>
       </c>
       <c r="O9" s="1">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="P9" s="1">
-        <v>180</v>
+        <v>325</v>
       </c>
       <c r="Q9" s="1">
-        <v>475</v>
+        <v>600</v>
       </c>
       <c r="R9" s="1">
-        <v>1400</v>
-      </c>
-      <c r="S9" s="1">
-        <v>0</v>
-      </c>
-      <c r="T9" s="1">
-        <v>950</v>
-      </c>
-      <c r="U9" s="1">
-        <v>325</v>
-      </c>
-      <c r="V9" s="1">
         <v>600</v>
       </c>
-      <c r="W9" s="1">
-        <v>600</v>
-      </c>
     </row>
-    <row r="10" spans="1:23" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="B10" s="1">
         <v>0</v>
@@ -1582,31 +1334,31 @@
         <v>0</v>
       </c>
       <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
         <v>0.25</v>
       </c>
-      <c r="I10" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="J10" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0</v>
-      </c>
-      <c r="L10" s="1">
-        <v>0</v>
-      </c>
-      <c r="M10" s="1">
-        <v>0</v>
-      </c>
-      <c r="N10" s="1">
-        <v>0</v>
-      </c>
-      <c r="O10" s="1">
-        <v>0.35</v>
-      </c>
       <c r="P10" s="1">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="Q10" s="1">
         <v>0</v>
@@ -1614,25 +1366,10 @@
       <c r="R10" s="1">
         <v>0</v>
       </c>
-      <c r="S10" s="1">
-        <v>0</v>
-      </c>
-      <c r="T10" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="U10" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="V10" s="1">
-        <v>0</v>
-      </c>
-      <c r="W10" s="1">
-        <v>0</v>
-      </c>
     </row>
-    <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="B11" s="1">
         <v>0</v>
@@ -1653,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
@@ -1674,36 +1411,21 @@
         <v>0</v>
       </c>
       <c r="O11" s="1">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="P11" s="1">
-        <v>0</v>
+        <v>325</v>
       </c>
       <c r="Q11" s="1">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="R11" s="1">
-        <v>0</v>
-      </c>
-      <c r="S11" s="1">
-        <v>0</v>
-      </c>
-      <c r="T11" s="1">
-        <v>120</v>
-      </c>
-      <c r="U11" s="1">
-        <v>325</v>
-      </c>
-      <c r="V11" s="1">
-        <v>300</v>
-      </c>
-      <c r="W11" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1">
         <v>0</v>
@@ -1724,16 +1446,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="I12" s="1">
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="K12" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L12" s="1">
         <v>0</v>
@@ -1745,10 +1467,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="1">
-        <v>1200</v>
+        <v>2600</v>
       </c>
       <c r="P12" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="1">
         <v>0</v>
@@ -1756,25 +1478,10 @@
       <c r="R12" s="1">
         <v>0</v>
       </c>
-      <c r="S12" s="1">
-        <v>0</v>
-      </c>
-      <c r="T12" s="1">
-        <v>2600</v>
-      </c>
-      <c r="U12" s="1">
-        <v>0</v>
-      </c>
-      <c r="V12" s="1">
-        <v>0</v>
-      </c>
-      <c r="W12" s="1">
-        <v>0</v>
-      </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1">
         <v>0</v>
@@ -1792,7 +1499,7 @@
         <v>500</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H13" s="1">
         <v>0</v>
@@ -1807,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="1">
-        <v>400</v>
+        <v>475</v>
       </c>
       <c r="M13" s="1">
         <v>0</v>
@@ -1822,24 +1529,9 @@
         <v>0</v>
       </c>
       <c r="Q13" s="1">
-        <v>475</v>
+        <v>650</v>
       </c>
       <c r="R13" s="1">
-        <v>0</v>
-      </c>
-      <c r="S13" s="1">
-        <v>0</v>
-      </c>
-      <c r="T13" s="1">
-        <v>0</v>
-      </c>
-      <c r="U13" s="1">
-        <v>0</v>
-      </c>
-      <c r="V13" s="1">
-        <v>650</v>
-      </c>
-      <c r="W13" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Configs/SkillConfig.xlsx
+++ b/Assets/Resources/Configs/SkillConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProgram\SoulFighterSurvivor\Assets\Resources\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CDB8B9E-F417-4F74-A3F1-3FDEB23CC9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88BAACCE-2CDB-4D7D-880C-8CBA721778D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="25845" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1384,7 +1384,7 @@
         <v>120</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -1402,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M11" s="1">
         <v>0</v>
@@ -1417,7 +1417,7 @@
         <v>325</v>
       </c>
       <c r="Q11" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="R11" s="1">
         <v>600</v>
